--- a/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
+++ b/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmissionStatus</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-18T09:05:02+00:00</t>
+    <t>2025-04-24T12:12:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,6 +256,9 @@
 </t>
   </si>
   <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -291,9 +294,6 @@
   <si>
     <t xml:space="preserve">Extension
 </t>
-  </si>
-  <si>
-    <t>An Extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -1073,7 +1073,7 @@
         <v>30</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1133,10 +1133,10 @@
         <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>76</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1158,7 +1158,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -1170,13 +1170,13 @@
         <v>76</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1227,13 +1227,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1242,15 +1242,15 @@
         <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1273,13 +1273,13 @@
         <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1342,7 +1342,7 @@
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -1361,10 +1361,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
@@ -1438,10 +1438,10 @@
         <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
@@ -1466,10 +1466,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -1542,7 +1542,7 @@
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
@@ -1569,10 +1569,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -1647,7 +1647,7 @@
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>76</v>
@@ -1675,7 +1675,7 @@
         <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>76</v>
@@ -1687,13 +1687,13 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1744,13 +1744,13 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>76</v>
@@ -1759,7 +1759,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -1790,7 +1790,7 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>116</v>
@@ -1861,10 +1861,10 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1880,10 +1880,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>76</v>
@@ -1990,7 +1990,7 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>76</v>
@@ -2002,13 +2002,13 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2059,13 +2059,13 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>76</v>
@@ -2074,7 +2074,7 @@
         <v>76</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -2105,7 +2105,7 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>116</v>
@@ -2176,10 +2176,10 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -2198,7 +2198,7 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -2277,7 +2277,7 @@
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
@@ -2305,7 +2305,7 @@
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>76</v>
@@ -2317,7 +2317,7 @@
         <v>121</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>144</v>
@@ -2382,7 +2382,7 @@
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>76</v>
@@ -2407,10 +2407,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>76</v>
@@ -2487,7 +2487,7 @@
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
@@ -2515,7 +2515,7 @@
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>76</v>
@@ -2527,7 +2527,7 @@
         <v>121</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>159</v>
@@ -2592,7 +2592,7 @@
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>76</v>
@@ -2620,7 +2620,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
@@ -2699,7 +2699,7 @@
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
@@ -2727,7 +2727,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -2739,7 +2739,7 @@
         <v>121</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>175</v>
@@ -2806,7 +2806,7 @@
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>

--- a/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
+++ b/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:12:45+00:00</t>
+    <t>2025-04-24T12:14:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
+++ b/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:14:49+00:00</t>
+    <t>2025-04-24T12:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
+++ b/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="182">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/preadmissionStatus</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:53:37+00:00</t>
+    <t>2025-04-25T09:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,6 +358,12 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>PreAdmissionStatusValueSet</t>
+  </si>
+  <si>
     <t>Extension.value[x]:valueCodeableConcept.id</t>
   </si>
   <si>
@@ -442,9 +448,6 @@
   </si>
   <si>
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/CodeSystem/preadmission-status</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -913,7 +916,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="23.55859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1617,13 +1620,11 @@
         <v>76</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y7" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y7" s="2"/>
       <c r="Z7" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>76</v>
@@ -1661,10 +1662,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1764,14 +1765,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1793,13 +1794,13 @@
         <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1869,10 +1870,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1892,22 +1893,22 @@
         <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -1956,7 +1957,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -1971,15 +1972,15 @@
         <v>108</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2079,14 +2080,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2108,13 +2109,13 @@
         <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2184,10 +2185,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2207,22 +2208,22 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K13" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -2232,7 +2233,7 @@
         <v>76</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>76</v>
@@ -2271,7 +2272,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2286,15 +2287,15 @@
         <v>108</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2314,19 +2315,19 @@
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2376,7 +2377,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2391,15 +2392,15 @@
         <v>108</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2419,20 +2420,20 @@
         <v>76</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2481,7 +2482,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2496,15 +2497,15 @@
         <v>108</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2524,20 +2525,20 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2586,7 +2587,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2601,15 +2602,15 @@
         <v>108</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2629,22 +2630,22 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -2693,7 +2694,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -2708,15 +2709,15 @@
         <v>108</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2736,22 +2737,22 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>85</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -2800,7 +2801,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -2815,7 +2816,7 @@
         <v>108</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
+++ b/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
+    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T09:56:34+00:00</t>
+    <t>2025-04-25T14:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
+++ b/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T14:29:23+00:00</t>
+    <t>2025-04-25T16:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
+++ b/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://github.com/Interop-Sante/hl7.fhir.fr.preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
+    <t>http://hl7.fr/fhir/fr/preadmission/StructureDefinition/hl7.fhir.fr.preadmission.statut-preadmission</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T16:50:14+00:00</t>
+    <t>2025-04-28T06:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
+++ b/nmoreau/ig/StructureDefinition-hl7.fhir.fr.preadmission.statut-preadmission.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T06:55:35+00:00</t>
+    <t>2025-04-28T10:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
